--- a/artfynd/A 1879-2026 artfynd.xlsx
+++ b/artfynd/A 1879-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113232864</v>
+        <v>113232667</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54271, Ytterhult, Sm</t>
+          <t>Ytterhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598246</v>
+        <v>598096</v>
       </c>
       <c r="R2" t="n">
-        <v>6394951</v>
+        <v>6394992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -794,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113232936</v>
+        <v>113232775</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,26 +795,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598263</v>
+        <v>598158</v>
       </c>
       <c r="R3" t="n">
-        <v>6394935</v>
+        <v>6394889</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,6 +890,338 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113232936</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 54271, Ytterhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598263</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6394935</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113232952</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 54271, Ytterhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598280</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6394912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113232864</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 54271, Ytterhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598246</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6394951</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
